--- a/DATE FUNCTION.xlsx
+++ b/DATE FUNCTION.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHANU SURYAVANSHI\Desktop\new Excel Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA9ADC4-8A3A-45CE-82CF-913A3AE7BDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757343D9-350C-4526-A089-6F923290AA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="date function" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>OrderID</t>
   </si>
@@ -105,6 +106,27 @@
   </si>
   <si>
     <t>month</t>
+  </si>
+  <si>
+    <t>EDATE()</t>
+  </si>
+  <si>
+    <t>EOMONTH()</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>HOLIDAY</t>
+  </si>
+  <si>
+    <t>NETWORKDAYS()</t>
+  </si>
+  <si>
+    <t>NETWORKDAYS.INTL</t>
+  </si>
+  <si>
+    <t>NETWORKDAYS/NETWORKDAYS.INTL</t>
   </si>
 </sst>
 </file>
@@ -112,9 +134,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +154,30 @@
       <sz val="10"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -147,12 +193,285 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="22">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thick">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color theme="1"/>
+      </right>
+      <top style="thick">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -160,24 +479,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,318 +819,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>101</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>45296</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>45297</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>45301</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>45296</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>1200</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="H2" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>102</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>45306</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>45308</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>45313</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>45307</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>850</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="H3" s="7">
+        <f>EDATE(B2,2)</f>
+        <v>45356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>103</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>45350</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>45351</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>45356</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>45350</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>104</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>45382</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>45383</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>45389</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>45382</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>980</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="H5" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>45453</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>45455</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>45461</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>45454</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>2200</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+      <c r="H6" s="7">
+        <f>EOMONTH(B2,2)</f>
+        <v>45382</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="6">
         <f>DAY(B2)</f>
         <v>5</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <f>MONTH(C2)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="6">
         <f>YEAR(D2)</f>
         <v>2024</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <f ca="1">TODAY()</f>
-        <v>46055</v>
-      </c>
-      <c r="F10" s="7">
+        <v>46056</v>
+      </c>
+      <c r="F10" s="8">
         <f ca="1">NOW()</f>
-        <v>46055.43646597222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="10" t="s">
+        <v>46056.411453356479</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B13">
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="10">
         <f ca="1">WEEKDAY(E10,2)</f>
-        <v>1</v>
-      </c>
-      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="C13" s="10">
         <f ca="1">WEEKNUM(E10,2)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
+    <row r="14" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="22"/>
+      <c r="G14" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="27"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="10" t="s">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="28"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17">
+      <c r="G16" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="29"/>
+    </row>
+    <row r="17" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="10">
         <v>13</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="10">
         <v>8</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="10">
         <v>2012</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <f>DATE(D17,C17,B17)</f>
         <v>41134</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
+      <c r="G17" s="13">
+        <v>46023</v>
+      </c>
+      <c r="H17" s="13">
+        <v>46032</v>
+      </c>
+      <c r="I17" s="12">
+        <f>NETWORKDAYS(G17,G18,H17:H19)</f>
+        <v>20</v>
+      </c>
+      <c r="J17" s="14">
+        <f>NETWORKDAYS.INTL(G17,G18,11,H17:H19)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G18" s="19">
+        <v>46053</v>
+      </c>
+      <c r="H18" s="18">
+        <v>46048</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="6"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="8">
+      <c r="C19" s="11"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="13">
+        <v>46036</v>
+      </c>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="7">
         <f ca="1">TODAY()</f>
-        <v>46055</v>
-      </c>
-      <c r="C20" t="str">
+        <v>46056</v>
+      </c>
+      <c r="C20" s="10" t="str">
         <f ca="1">TEXT(B20,"DD MMM YYYY")</f>
-        <v>02 Feb 2026</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C21" t="str">
+        <v>03 Feb 2026</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10" t="str">
         <f ca="1">TEXT(B20,"DD/MM/YY")</f>
-        <v>02/02/26</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C22" t="str">
+        <v>03/02/26</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10" t="str">
         <f ca="1">TEXT(B20,"DDDD , (DD MMM  YYYY)")</f>
-        <v>Monday , (02 Feb  2026)</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C23" t="str">
+        <v>Tuesday , (03 Feb  2026)</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10" t="str">
         <f ca="1">PROPER("today is "&amp; TEXT(B20,"dddd dd mmm ,yyyy"))</f>
-        <v>Today Is Monday 02 Feb ,2026</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="6" t="s">
+        <v>Today Is Tuesday 03 Feb ,2026</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="8">
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="7">
         <v>37215</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <f ca="1">TODAY()</f>
-        <v>46055</v>
-      </c>
-      <c r="D27">
+        <v>46056</v>
+      </c>
+      <c r="D27" s="10">
         <f ca="1">DATEDIF(B27,C27,"y")</f>
         <v>24</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D28">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10">
         <f ca="1">DATEDIF(B27,C27,"d")</f>
-        <v>8840</v>
-      </c>
-      <c r="E28" t="s">
+        <v>8841</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D29">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10">
         <f ca="1">DATEDIF(B27,C27,"m")</f>
         <v>290</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D30" t="str">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10" t="str">
         <f ca="1">PROPER(DATEDIF(B27,C27,"y")&amp;" YEAR " &amp; DATEDIF(B27,C27,"YM")&amp;" MONTH " &amp; DATEDIF(B27,C27,"MD") &amp; " DAY ")</f>
-        <v xml:space="preserve">24 Year 2 Month 13 Day </v>
-      </c>
+        <v xml:space="preserve">24 Year 2 Month 14 Day </v>
+      </c>
+      <c r="E30" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G14:J15"/>
+    <mergeCell ref="B26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BF1B88-0F69-442E-83E4-4B567F959325}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>